--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_11_15.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_11_15.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>175285.9083031516</v>
+        <v>178187.4507680243</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11080148.26208699</v>
+        <v>11080496.12760381</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21901350.13187793</v>
+        <v>21901388.32567452</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3975821.807726725</v>
+        <v>3975759.944993741</v>
       </c>
     </row>
     <row r="11">
@@ -7959,22 +7959,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>208.3282982811614</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L2" t="n">
-        <v>221.1751687388314</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M2" t="n">
-        <v>214.1106603629511</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N2" t="n">
-        <v>212.9147821895557</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O2" t="n">
-        <v>214.5193521252043</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P2" t="n">
-        <v>217.93679977537</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q2" t="n">
         <v>212.3149906599047</v>
@@ -8035,28 +8035,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J3" t="n">
-        <v>122.1636361006289</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K3" t="n">
-        <v>129.8528446347364</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L3" t="n">
-        <v>127.8127288364779</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M3" t="n">
-        <v>129.5990339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N3" t="n">
-        <v>118.4749479323899</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O3" t="n">
-        <v>130.8256689727463</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P3" t="n">
-        <v>124.5274828860284</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q3" t="n">
-        <v>133.666755218097</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8120,19 +8120,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L4" t="n">
-        <v>128.7184139861563</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M4" t="n">
-        <v>132.4243249312116</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N4" t="n">
-        <v>121.3386756127742</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O4" t="n">
-        <v>132.5941777961051</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P4" t="n">
-        <v>132.7117417540657</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q4" t="n">
         <v>65.34295837775146</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>105.2992814111083</v>
+        <v>105.2660364171859</v>
       </c>
       <c r="K5" t="n">
-        <v>106.5652982811613</v>
+        <v>106.5154726531473</v>
       </c>
       <c r="L5" t="n">
-        <v>94.92916873883132</v>
+        <v>94.86735564139641</v>
       </c>
       <c r="M5" t="n">
-        <v>73.63766036295098</v>
+        <v>73.56888138194589</v>
       </c>
       <c r="N5" t="n">
-        <v>70.1687821895556</v>
+        <v>70.0988902927316</v>
       </c>
       <c r="O5" t="n">
-        <v>79.72835212520417</v>
+        <v>79.66235518893416</v>
       </c>
       <c r="P5" t="n">
-        <v>102.8957997753699</v>
+        <v>102.8394729171565</v>
       </c>
       <c r="Q5" t="n">
-        <v>125.9298004272132</v>
+        <v>125.8875013024845</v>
       </c>
       <c r="R5" t="n">
         <v>65.71641987298243</v>
@@ -8272,28 +8272,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J6" t="n">
-        <v>81.72345685534589</v>
+        <v>81.70365636471669</v>
       </c>
       <c r="K6" t="n">
-        <v>60.73413708756647</v>
+        <v>60.70029489530543</v>
       </c>
       <c r="L6" t="n">
-        <v>34.87409676100616</v>
+        <v>34.82859175712527</v>
       </c>
       <c r="M6" t="n">
-        <v>21.14403392201822</v>
+        <v>21.0909317288216</v>
       </c>
       <c r="N6" t="n">
-        <v>7.149466800314315</v>
+        <v>7.094959150074288</v>
       </c>
       <c r="O6" t="n">
-        <v>28.98460293501036</v>
+        <v>28.93473908397459</v>
       </c>
       <c r="P6" t="n">
-        <v>42.79104892376412</v>
+        <v>42.75102878723314</v>
       </c>
       <c r="Q6" t="n">
-        <v>79.02811370866297</v>
+        <v>79.00136130722979</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8351,28 +8351,28 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K7" t="n">
-        <v>82.50243849840422</v>
+        <v>82.48202502181968</v>
       </c>
       <c r="L7" t="n">
-        <v>75.36684021566445</v>
+        <v>75.34071799375025</v>
       </c>
       <c r="M7" t="n">
-        <v>76.17257083285091</v>
+        <v>76.14502861244816</v>
       </c>
       <c r="N7" t="n">
-        <v>66.42446249801998</v>
+        <v>66.39757517005853</v>
       </c>
       <c r="O7" t="n">
-        <v>81.87201386167878</v>
+        <v>81.84717906246624</v>
       </c>
       <c r="P7" t="n">
-        <v>89.31016798357382</v>
+        <v>89.28891752250335</v>
       </c>
       <c r="Q7" t="n">
-        <v>65.34295837775143</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -8430,28 +8430,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>92.67484422517873</v>
+        <v>92.06191329280011</v>
       </c>
       <c r="K8" t="n">
-        <v>87.64453948719154</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L8" t="n">
-        <v>71.45629436697212</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M8" t="n">
-        <v>47.51956488556419</v>
+        <v>46.25150133729363</v>
       </c>
       <c r="N8" t="n">
-        <v>43.62806862171652</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O8" t="n">
-        <v>54.66670890912388</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P8" t="n">
-        <v>81.50626711205342</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q8" t="n">
-        <v>109.8671521860073</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R8" t="n">
         <v>65.71641987298243</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>74.20442855345914</v>
+        <v>73.83937108913167</v>
       </c>
       <c r="K9" t="n">
-        <v>47.88292010643443</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L9" t="n">
-        <v>17.59404959119487</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9790339220182886</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>10.04932935010476</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P9" t="n">
-        <v>27.59382250866982</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q9" t="n">
-        <v>68.86917031243658</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8591,22 +8591,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K10" t="n">
-        <v>74.75063521971572</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L10" t="n">
-        <v>65.44720087140219</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M10" t="n">
-        <v>65.71370198039193</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N10" t="n">
-        <v>56.21428217015117</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O10" t="n">
-        <v>72.44125976331816</v>
+        <v>71.98338581476828</v>
       </c>
       <c r="P10" t="n">
-        <v>81.24052863931158</v>
+        <v>80.84873837615825</v>
       </c>
       <c r="Q10" t="n">
         <v>65.34295837775146</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>71.86158291864589</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K11" t="n">
-        <v>56.45085607010591</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L11" t="n">
-        <v>32.75777175390647</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M11" t="n">
-        <v>4.460002071493449</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13.34886468801804</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P11" t="n">
-        <v>46.24244299145019</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q11" t="n">
-        <v>83.38548886942414</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,10 +8746,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>61.80819270440242</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K12" t="n">
-        <v>26.69577859700033</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -8764,10 +8764,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.538935716216798</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.12064201054967</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8825,28 +8825,28 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>61.97063521971562</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L13" t="n">
-        <v>49.09320087140209</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M13" t="n">
-        <v>48.47070198039184</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N13" t="n">
-        <v>39.38128217015104</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O13" t="n">
-        <v>56.89325976331806</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P13" t="n">
-        <v>67.93652863931148</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.34295837775143</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>71.86158291864584</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K14" t="n">
-        <v>56.45085607010586</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L14" t="n">
-        <v>32.75777175390641</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M14" t="n">
-        <v>4.460002071493392</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>13.34886468801793</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P14" t="n">
-        <v>46.24244299145008</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q14" t="n">
-        <v>83.38548886942411</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,10 +8983,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>61.8081927044024</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K15" t="n">
-        <v>26.69577859700027</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -9001,10 +9001,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.53893571621677</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.12064201054962</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>61.9706352197156</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L16" t="n">
-        <v>49.09320087140206</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M16" t="n">
-        <v>48.47070198039178</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N16" t="n">
-        <v>39.38128217015098</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O16" t="n">
-        <v>56.89325976331803</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P16" t="n">
-        <v>67.93652863931146</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>71.86158291876362</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K17" t="n">
-        <v>56.45085607022344</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L17" t="n">
-        <v>32.75777175402388</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M17" t="n">
-        <v>4.460002071610973</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.006126457338019e-12</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>13.34886468813545</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P17" t="n">
-        <v>46.24244299156766</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q17" t="n">
-        <v>83.38548886954166</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>61.80819270452015</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K18" t="n">
-        <v>26.69577859711805</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.554934538551606e-12</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-8.469669410260394e-12</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.72546479513403e-12</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.538935716334407</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.1206420106674</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9299,25 +9299,25 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>61.97063521983341</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L19" t="n">
-        <v>49.09320087151976</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M19" t="n">
-        <v>48.47070198050956</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N19" t="n">
-        <v>39.38128217026875</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O19" t="n">
-        <v>56.89325976343575</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P19" t="n">
-        <v>67.93652863942924</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>71.86158291864558</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K20" t="n">
-        <v>56.45085607010535</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L20" t="n">
-        <v>32.75777175390596</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M20" t="n">
-        <v>4.46000207149288</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>13.34886468801741</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P20" t="n">
-        <v>46.24244299144962</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q20" t="n">
-        <v>83.38548886942365</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,10 +9457,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>61.80819270440217</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K21" t="n">
-        <v>26.69577859700001</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -9475,10 +9475,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.538935716216315</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.12064201054939</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9536,25 +9536,25 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>61.97063521971538</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L22" t="n">
-        <v>49.09320087140181</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M22" t="n">
-        <v>48.47070198039155</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N22" t="n">
-        <v>39.38128217015075</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O22" t="n">
-        <v>56.89325976331777</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P22" t="n">
-        <v>67.93652863931123</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>71.86158291864535</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K23" t="n">
-        <v>56.45085607010535</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L23" t="n">
-        <v>32.75777175390573</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M23" t="n">
-        <v>4.460002071492426</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>13.34886468801696</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P23" t="n">
-        <v>46.24244299144951</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q23" t="n">
-        <v>83.38548886942354</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,10 +9694,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>61.80819270440212</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K24" t="n">
-        <v>26.69577859699979</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.538935716216201</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.12064201054933</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9773,25 +9773,25 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>61.97063521971532</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L25" t="n">
-        <v>49.09320087140181</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M25" t="n">
-        <v>48.4707019803915</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N25" t="n">
-        <v>39.3812821701507</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O25" t="n">
-        <v>56.89325976331777</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P25" t="n">
-        <v>67.93652863931118</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>71.86158291877385</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K26" t="n">
-        <v>56.4508560702335</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L26" t="n">
-        <v>32.75777175403351</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M26" t="n">
-        <v>4.460002071620465</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>13.34886468814497</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P26" t="n">
-        <v>46.24244299157766</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q26" t="n">
-        <v>83.38548886955184</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,16 +9931,16 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>61.80819270453087</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K27" t="n">
-        <v>26.69577859712828</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.940790127410207e-12</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.538935716344582</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q27" t="n">
-        <v>52.12064201067788</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10010,25 +10010,25 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>61.97063521984398</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L28" t="n">
-        <v>49.09320087153027</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M28" t="n">
-        <v>48.47070198052005</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N28" t="n">
-        <v>39.38128217027926</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O28" t="n">
-        <v>56.8932597634463</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P28" t="n">
-        <v>67.93652863943984</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>71.861582918869</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K29" t="n">
-        <v>56.45085607032831</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L29" t="n">
-        <v>32.75777175412844</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M29" t="n">
-        <v>4.460002071715053</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.332447658551704e-11</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>13.34886468824001</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P29" t="n">
-        <v>46.24244299167214</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q29" t="n">
-        <v>83.38548886964676</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,13 +10168,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>61.80819270462611</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K30" t="n">
-        <v>26.69577859723813</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L30" t="n">
-        <v>-1.656985659792554e-11</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.708144736767281e-11</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.538935716439624</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q30" t="n">
-        <v>52.12064201077304</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10247,25 +10247,25 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>61.97063521993937</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L31" t="n">
-        <v>49.09320087162548</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M31" t="n">
-        <v>48.4707019806152</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N31" t="n">
-        <v>39.38128217037439</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O31" t="n">
-        <v>56.89325976354156</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P31" t="n">
-        <v>67.93652863953517</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>71.86158291883339</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K32" t="n">
-        <v>56.45085607029179</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L32" t="n">
-        <v>32.75777175409146</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M32" t="n">
-        <v>4.460002071677792</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>13.34886468820258</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P32" t="n">
-        <v>46.24244299163561</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q32" t="n">
-        <v>83.38548886961064</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>61.80819270459072</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K33" t="n">
-        <v>26.69577859717302</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.449154726889458e-11</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.432454155292362e-11</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.538935716403387</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q33" t="n">
-        <v>52.1206420107376</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10484,25 +10484,25 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>61.97063521990384</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L34" t="n">
-        <v>49.09320087158953</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M34" t="n">
-        <v>48.47070198057976</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N34" t="n">
-        <v>39.38128217033898</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O34" t="n">
-        <v>56.8932597635055</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P34" t="n">
-        <v>67.9365286394997</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>71.86158291892141</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K35" t="n">
-        <v>56.45085607038084</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L35" t="n">
-        <v>32.75777175418054</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M35" t="n">
-        <v>4.460002071767974</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N35" t="n">
-        <v>-1.808932618359312e-11</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>13.34886468829211</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P35" t="n">
-        <v>46.24244299172511</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q35" t="n">
-        <v>83.38548886969906</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,10 +10642,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>61.80819270467835</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K36" t="n">
-        <v>26.69577859727582</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -10660,10 +10660,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.538935716492119</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q36" t="n">
-        <v>52.12064201082539</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10721,25 +10721,25 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>61.97063521999146</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L37" t="n">
-        <v>49.09320087167735</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M37" t="n">
-        <v>48.47070198066756</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N37" t="n">
-        <v>39.38128217042677</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O37" t="n">
-        <v>56.89325976359332</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P37" t="n">
-        <v>67.93652863958721</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>71.86158291904988</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K38" t="n">
-        <v>56.45085607050811</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L38" t="n">
-        <v>32.75777175430889</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M38" t="n">
-        <v>4.460002071894394</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>13.34886468841927</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P38" t="n">
-        <v>46.24244299185256</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q38" t="n">
-        <v>83.38548886982628</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>61.80819270480723</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K39" t="n">
-        <v>26.69577859740349</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.949070222678891e-11</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.950173438875936e-11</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>-3.319655661471188e-11</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.538935716620358</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q39" t="n">
-        <v>52.12064201095309</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>61.97063522011925</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L40" t="n">
-        <v>49.09320087180653</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M40" t="n">
-        <v>48.47070198079511</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N40" t="n">
-        <v>39.38128217055534</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O40" t="n">
-        <v>56.8932597637217</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P40" t="n">
-        <v>67.93652863971602</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>71.86158291924355</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K41" t="n">
-        <v>56.45085607070291</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L41" t="n">
-        <v>32.75777175450261</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M41" t="n">
-        <v>4.460002072089196</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>13.34886468861419</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P41" t="n">
-        <v>46.24244299204702</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q41" t="n">
-        <v>83.38548887002159</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,10 +11116,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>61.80819270500072</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K42" t="n">
-        <v>26.69577859759798</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11131,13 +11131,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>-3.060719212292283e-11</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.538935716814279</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q42" t="n">
-        <v>52.12064201114767</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11195,28 +11195,28 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>33.63624132272331</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>61.97063522031394</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L43" t="n">
-        <v>49.09320087200014</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M43" t="n">
-        <v>48.47070198098983</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N43" t="n">
-        <v>39.38128217074903</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O43" t="n">
-        <v>56.89325976391613</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P43" t="n">
-        <v>67.9365286399098</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q43" t="n">
-        <v>65.34295837775143</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>71.86158291929232</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K44" t="n">
-        <v>56.4508560707495</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L44" t="n">
-        <v>32.75777175454976</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M44" t="n">
-        <v>4.460002072135097</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N44" t="n">
-        <v>-3.050632828348922e-11</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>13.34886468865952</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P44" t="n">
-        <v>46.24244299209494</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q44" t="n">
-        <v>83.38548887006777</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>61.8081927050501</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K45" t="n">
-        <v>26.69577859758613</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L45" t="n">
-        <v>-3.421973815420643e-11</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-3.421973815420642e-11</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>-3.33386651618639e-11</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.538935716862767</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q45" t="n">
-        <v>52.12064201119493</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,25 +11435,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>61.97063522036146</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L46" t="n">
-        <v>49.09320087204917</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M46" t="n">
-        <v>48.4707019810371</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N46" t="n">
-        <v>39.38128217079813</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O46" t="n">
-        <v>56.89325976396354</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P46" t="n">
-        <v>67.93652863995899</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q46" t="n">
-        <v>65.34295837775143</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -22519,16 +22519,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G2" t="n">
-        <v>415.2102752035773</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H2" t="n">
-        <v>338.5278724675259</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I2" t="n">
-        <v>206.9112363040742</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J2" t="n">
-        <v>4.101666239034614</v>
+        <v>4.097100052852173</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -22549,19 +22549,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.005809767308619485</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>144.0609822627577</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S2" t="n">
-        <v>206.9130846616222</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T2" t="n">
-        <v>222.6910957952871</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U2" t="n">
-        <v>251.3382559229119</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V2" t="n">
         <v>327.7522584701349</v>
@@ -22598,13 +22598,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>137.2940454650974</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H3" t="n">
-        <v>111.7576517836663</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I3" t="n">
-        <v>87.69333096462262</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -22631,16 +22631,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>97.08624924698275</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S3" t="n">
-        <v>170.7642560094982</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T3" t="n">
-        <v>199.9653230344443</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U3" t="n">
-        <v>225.9381273639937</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V3" t="n">
         <v>232.8005871494253</v>
@@ -22677,19 +22677,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G4" t="n">
-        <v>167.9495039486227</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H4" t="n">
-        <v>161.8584184090789</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I4" t="n">
-        <v>154.2031962387337</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J4" t="n">
-        <v>90.42686864126296</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K4" t="n">
-        <v>17.45080330129268</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -22707,19 +22707,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>82.68904325169437</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R4" t="n">
-        <v>175.4285061312679</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S4" t="n">
-        <v>223.2937947582837</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T4" t="n">
-        <v>227.7683763135274</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U4" t="n">
-        <v>286.3167670614089</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V4" t="n">
         <v>252.137643323828</v>
@@ -22756,13 +22756,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G5" t="n">
-        <v>414.4102752035773</v>
+        <v>414.4098835042129</v>
       </c>
       <c r="H5" t="n">
-        <v>330.3348724675259</v>
+        <v>330.3308609764111</v>
       </c>
       <c r="I5" t="n">
-        <v>176.0692363040742</v>
+        <v>176.0541353143313</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -22789,16 +22789,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>93.80798226275768</v>
+        <v>93.78337717756372</v>
       </c>
       <c r="S5" t="n">
-        <v>188.6830846616222</v>
+        <v>188.6741588123578</v>
       </c>
       <c r="T5" t="n">
-        <v>219.1890957952871</v>
+        <v>219.1873811313198</v>
       </c>
       <c r="U5" t="n">
-        <v>251.2742559229119</v>
+        <v>251.2742245869627</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22835,13 +22835,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>136.8660077292484</v>
+        <v>136.8657981516121</v>
       </c>
       <c r="H6" t="n">
-        <v>107.6237083874398</v>
+        <v>107.6216843086893</v>
       </c>
       <c r="I6" t="n">
-        <v>72.95606681367921</v>
+        <v>72.94885109242954</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -22868,16 +22868,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>70.51036245452988</v>
+        <v>70.49735025707633</v>
       </c>
       <c r="S6" t="n">
-        <v>162.813642801951</v>
+        <v>162.8097499892768</v>
       </c>
       <c r="T6" t="n">
-        <v>198.2400305816141</v>
+        <v>198.2391858366678</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9099669866352</v>
+        <v>225.9099531986328</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -22914,16 +22914,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.5906514896063</v>
+        <v>167.5904757867562</v>
       </c>
       <c r="H7" t="n">
-        <v>158.667893818915</v>
+        <v>158.6663316608477</v>
       </c>
       <c r="I7" t="n">
-        <v>143.4115241075861</v>
+        <v>143.406240243694</v>
       </c>
       <c r="J7" t="n">
-        <v>65.05599978880392</v>
+        <v>65.04357759730172</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -22944,19 +22944,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>52.64004325169437</v>
+        <v>52.6253305339463</v>
       </c>
       <c r="R7" t="n">
-        <v>159.293194655858</v>
+        <v>159.285294416798</v>
       </c>
       <c r="S7" t="n">
-        <v>217.0399750861526</v>
+        <v>217.0369130646649</v>
       </c>
       <c r="T7" t="n">
-        <v>226.2350976250028</v>
+        <v>226.2343468946433</v>
       </c>
       <c r="U7" t="n">
-        <v>286.2971932909171</v>
+        <v>286.2971837071253</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -22993,13 +22993,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>414.2615314849843</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H8" t="n">
-        <v>328.8115508594857</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I8" t="n">
-        <v>170.334794093019</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -23026,16 +23026,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>84.46445964969242</v>
+        <v>84.01082088999308</v>
       </c>
       <c r="S8" t="n">
-        <v>185.293587174185</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T8" t="n">
-        <v>218.5379701671464</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U8" t="n">
-        <v>251.2623564254244</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,13 +23072,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>136.786422823588</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H9" t="n">
-        <v>106.8550857459304</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I9" t="n">
-        <v>70.21597247405658</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>65.56911717151105</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S9" t="n">
-        <v>161.3353880849699</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T9" t="n">
-        <v>197.9192475627461</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9047311375786</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,16 +23151,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.5239301781309</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H10" t="n">
-        <v>158.0746807041609</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I10" t="n">
-        <v>141.4050323043075</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J10" t="n">
-        <v>60.33880306749246</v>
+        <v>60.10977774604451</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23181,19 +23181,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>47.05304325169438</v>
+        <v>46.78178798155719</v>
       </c>
       <c r="R10" t="n">
-        <v>156.2931618689728</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S10" t="n">
-        <v>215.8772045943493</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T10" t="n">
-        <v>225.9500156577897</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U10" t="n">
-        <v>286.2935539466548</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H11" t="n">
-        <v>326.3001287489329</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I11" t="n">
-        <v>160.8807136910088</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>69.06027372004401</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S11" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T11" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H12" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I12" t="n">
-        <v>65.69851964386787</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>57.42273981302041</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S12" t="n">
-        <v>158.8982654434604</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T12" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U12" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H13" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I13" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J13" t="n">
-        <v>52.5618030674924</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37.84204325169431</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R13" t="n">
-        <v>151.3471618689727</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S13" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T13" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H14" t="n">
-        <v>326.3001287489329</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I14" t="n">
-        <v>160.8807136910088</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>69.06027372004401</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S14" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T14" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H15" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I15" t="n">
-        <v>65.69851964386785</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>57.42273981302039</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S15" t="n">
-        <v>158.8982654434604</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T15" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U15" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H16" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I16" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J16" t="n">
-        <v>52.56180306749238</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.84204325169428</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R16" t="n">
-        <v>151.3471618689727</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S16" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T16" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H17" t="n">
-        <v>326.3001287489329</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I17" t="n">
-        <v>160.8807136910087</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>69.06027372004378</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S17" t="n">
-        <v>179.7054967219236</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T17" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H18" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I18" t="n">
-        <v>65.6985196438678</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>57.42273981302027</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S18" t="n">
-        <v>158.8982654434604</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T18" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U18" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H19" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I19" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J19" t="n">
-        <v>52.56180306749228</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.84204325169416</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R19" t="n">
-        <v>151.3471618689727</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S19" t="n">
-        <v>213.9602045943492</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T19" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H20" t="n">
-        <v>326.3001287489329</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I20" t="n">
-        <v>160.8807136910087</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>69.06027372004372</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S20" t="n">
-        <v>179.7054967219236</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T20" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H21" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I21" t="n">
-        <v>65.6985196438678</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>57.42273981302027</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S21" t="n">
-        <v>158.8982654434604</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T21" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U21" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H22" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I22" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J22" t="n">
-        <v>52.56180306749226</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.84204325169416</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R22" t="n">
-        <v>151.3471618689727</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S22" t="n">
-        <v>213.9602045943492</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T22" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H23" t="n">
-        <v>326.3001287489329</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I23" t="n">
-        <v>160.8807136910087</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>69.06027372004372</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S23" t="n">
-        <v>179.7054967219235</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T23" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H24" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I24" t="n">
-        <v>65.69851964386777</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>57.42273981302027</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S24" t="n">
-        <v>158.8982654434604</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T24" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U24" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H25" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I25" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J25" t="n">
-        <v>52.56180306749226</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.84204325169411</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R25" t="n">
-        <v>151.3471618689726</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S25" t="n">
-        <v>213.9602045943492</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T25" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.016305354331</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H26" t="n">
-        <v>326.3001287489328</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I26" t="n">
-        <v>160.8807136910084</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>69.06027372004333</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S26" t="n">
-        <v>179.7054967219234</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T26" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H27" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I27" t="n">
-        <v>65.69851964386764</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>57.42273981302004</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S27" t="n">
-        <v>158.8982654434603</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T27" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U27" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H28" t="n">
-        <v>157.0966807041608</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I28" t="n">
-        <v>138.0970323043073</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J28" t="n">
-        <v>52.56180306749206</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37.84204325169385</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R28" t="n">
-        <v>151.3471618689725</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S28" t="n">
-        <v>213.9602045943492</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T28" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.016305354331</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H29" t="n">
-        <v>326.3001287489328</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I29" t="n">
-        <v>160.8807136910082</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>69.06027372004287</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S29" t="n">
-        <v>179.7054967219233</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T29" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H30" t="n">
-        <v>105.587897066685</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I30" t="n">
-        <v>65.69851964386753</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>57.42273981301979</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S30" t="n">
-        <v>158.8982654434603</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T30" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U30" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H31" t="n">
-        <v>157.0966807041608</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I31" t="n">
-        <v>138.0970323043072</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J31" t="n">
-        <v>52.56180306749183</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>37.84204325169362</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R31" t="n">
-        <v>151.3471618689724</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S31" t="n">
-        <v>213.9602045943491</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T31" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.016305354331</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H32" t="n">
-        <v>326.3001287489327</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I32" t="n">
-        <v>160.8807136910077</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>69.06027372004196</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S32" t="n">
-        <v>179.7054967219229</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T32" t="n">
-        <v>217.4644927802116</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H33" t="n">
-        <v>105.587897066685</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I33" t="n">
-        <v>65.6985196438673</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>57.42273981301939</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S33" t="n">
-        <v>158.8982654434601</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T33" t="n">
-        <v>197.39038907218</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U33" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H34" t="n">
-        <v>157.0966807041607</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I34" t="n">
-        <v>138.097032304307</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J34" t="n">
-        <v>52.56180306749138</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37.84204325169317</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R34" t="n">
-        <v>151.3471618689721</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S34" t="n">
-        <v>213.960204594349</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T34" t="n">
-        <v>225.4800156577896</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.016305354331</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H35" t="n">
-        <v>326.3001287489328</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I35" t="n">
-        <v>160.8807136910084</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>69.06027372004321</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S35" t="n">
-        <v>179.7054967219234</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T35" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H36" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I36" t="n">
-        <v>65.69851964386767</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>57.42273981302002</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S36" t="n">
-        <v>158.8982654434603</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T36" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U36" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H37" t="n">
-        <v>157.0966807041608</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I37" t="n">
-        <v>138.0970323043072</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J37" t="n">
-        <v>52.561803067492</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>37.84204325169385</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R37" t="n">
-        <v>151.3471618689725</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S37" t="n">
-        <v>213.9602045943492</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T37" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.016305354331</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H38" t="n">
-        <v>326.3001287489327</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I38" t="n">
-        <v>160.8807136910079</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>69.06027372004259</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S38" t="n">
-        <v>179.7054967219231</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T38" t="n">
-        <v>217.4644927802116</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H39" t="n">
-        <v>105.587897066685</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I39" t="n">
-        <v>65.69851964386741</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>57.42273981301962</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S39" t="n">
-        <v>158.8982654434602</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T39" t="n">
-        <v>197.39038907218</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U39" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H40" t="n">
-        <v>157.0966807041608</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I40" t="n">
-        <v>138.0970323043071</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J40" t="n">
-        <v>52.56180306749167</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>37.8420432516934</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R40" t="n">
-        <v>151.3471618689723</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S40" t="n">
-        <v>213.9602045943491</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T40" t="n">
-        <v>225.4800156577896</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.016305354331</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H41" t="n">
-        <v>326.3001287489328</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I41" t="n">
-        <v>160.8807136910081</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>69.06027372004293</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S41" t="n">
-        <v>179.7054967219233</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T41" t="n">
-        <v>217.4644927802117</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H42" t="n">
-        <v>105.587897066685</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I42" t="n">
-        <v>65.69851964386756</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>57.42273981301985</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S42" t="n">
-        <v>158.8982654434603</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T42" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U42" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H43" t="n">
-        <v>157.0966807041608</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I43" t="n">
-        <v>138.0970323043072</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J43" t="n">
-        <v>52.56180306749186</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>37.84204325169368</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R43" t="n">
-        <v>151.3471618689724</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S43" t="n">
-        <v>213.9602045943492</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T43" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.016305354331</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H44" t="n">
-        <v>326.3001287489326</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I44" t="n">
-        <v>160.8807136910077</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>69.06027372004202</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S44" t="n">
-        <v>179.7054967219229</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T44" t="n">
-        <v>217.4644927802116</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H45" t="n">
-        <v>105.5878970666849</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I45" t="n">
-        <v>65.69851964386729</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>57.42273981301933</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S45" t="n">
-        <v>158.8982654434601</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T45" t="n">
-        <v>197.39038907218</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U45" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H46" t="n">
-        <v>157.0966807041607</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I46" t="n">
-        <v>138.097032304307</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J46" t="n">
-        <v>52.56180306749139</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>37.84204325169314</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R46" t="n">
-        <v>151.347161868972</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S46" t="n">
-        <v>213.9602045943491</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T46" t="n">
-        <v>225.4800156577896</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>356179.5652298389</v>
+        <v>356180.2897140363</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>346267.6860484236</v>
+        <v>346262.2304563036</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>344353.9664017614</v>
+        <v>344265.1004727246</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>342089.233555646</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>342089.233555646</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342089.2335556738</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>342089.233555646</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>342089.233555646</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>342089.2335556766</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>342089.2335556993</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>342089.233555691</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>342089.2335557117</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>342089.233555742</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>342089.2335557892</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>342089.2335557987</v>
+        <v>342092.0939925317</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81828.19351646857</v>
+        <v>81828.86921158248</v>
       </c>
       <c r="C2" t="n">
-        <v>87174.63166972371</v>
+        <v>87177.11248431254</v>
       </c>
       <c r="D2" t="n">
-        <v>88116.69494759256</v>
+        <v>88162.43320227742</v>
       </c>
       <c r="E2" t="n">
-        <v>89669.82629759259</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="F2" t="n">
-        <v>89669.8262975926</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="G2" t="n">
-        <v>89669.82629764215</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="H2" t="n">
-        <v>89669.82629759259</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="I2" t="n">
-        <v>89669.8262975926</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="J2" t="n">
-        <v>89669.82629764677</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="K2" t="n">
-        <v>89669.82629768728</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="L2" t="n">
-        <v>89669.82629767225</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="M2" t="n">
-        <v>89669.82629770873</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="N2" t="n">
-        <v>89669.82629776305</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="O2" t="n">
-        <v>89669.82629784435</v>
+        <v>89665.27431143694</v>
       </c>
       <c r="P2" t="n">
-        <v>89669.82629786422</v>
+        <v>89665.27431143692</v>
       </c>
     </row>
     <row r="3">
@@ -26313,16 +26313,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22163.099</v>
+        <v>22175.99473096512</v>
       </c>
       <c r="C3" t="n">
-        <v>181209.798</v>
+        <v>181286.3364020008</v>
       </c>
       <c r="D3" t="n">
-        <v>31687.318</v>
+        <v>33142.32881762755</v>
       </c>
       <c r="E3" t="n">
-        <v>49007.583</v>
+        <v>47420.72226727413</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56142.855669454</v>
+        <v>55206.51629369851</v>
       </c>
       <c r="C4" t="n">
-        <v>26627.36992610333</v>
+        <v>26169.79188387299</v>
       </c>
       <c r="D4" t="n">
-        <v>21259.41826058873</v>
+        <v>20653.20901911422</v>
       </c>
       <c r="E4" t="n">
-        <v>13299.87046447302</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="F4" t="n">
-        <v>13299.87046447301</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="G4" t="n">
-        <v>13299.87046450069</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="H4" t="n">
-        <v>13299.87046447292</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="I4" t="n">
-        <v>13299.87046447288</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="J4" t="n">
-        <v>13299.8704645035</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="K4" t="n">
-        <v>13299.87046452581</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="L4" t="n">
-        <v>13299.87046451713</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="M4" t="n">
-        <v>13299.87046453847</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="N4" t="n">
-        <v>13299.87046456839</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="O4" t="n">
-        <v>13299.87046461565</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="P4" t="n">
-        <v>13299.8704646248</v>
+        <v>13097.69183178116</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34129</v>
+        <v>34129.29174257201</v>
       </c>
       <c r="C5" t="n">
-        <v>38467.2</v>
+        <v>38469.32408772787</v>
       </c>
       <c r="D5" t="n">
-        <v>39273.8</v>
+        <v>39312.96135688073</v>
       </c>
       <c r="E5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="F5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="G5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="H5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="I5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="J5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="K5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="L5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="M5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="N5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="O5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="P5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-30606.76115298543</v>
+        <v>-29682.93355565316</v>
       </c>
       <c r="C6" t="n">
-        <v>-159129.7362563796</v>
+        <v>-158748.3398892891</v>
       </c>
       <c r="D6" t="n">
-        <v>-4103.841312996163</v>
+        <v>-4946.065991345087</v>
       </c>
       <c r="E6" t="n">
-        <v>20386.37283311957</v>
+        <v>22174.75764912431</v>
       </c>
       <c r="F6" t="n">
-        <v>69393.9558331196</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="G6" t="n">
-        <v>69393.95583314146</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="H6" t="n">
-        <v>69393.95583311967</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="I6" t="n">
-        <v>69393.95583311973</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="J6" t="n">
-        <v>69393.95583314326</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="K6" t="n">
-        <v>69393.95583316147</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="L6" t="n">
-        <v>69393.95583315511</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="M6" t="n">
-        <v>69393.95583317026</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="N6" t="n">
-        <v>69393.95583319466</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="O6" t="n">
-        <v>69393.9558332287</v>
+        <v>69595.47991639844</v>
       </c>
       <c r="P6" t="n">
-        <v>69393.95583323942</v>
+        <v>69595.47991639843</v>
       </c>
     </row>
   </sheetData>
@@ -26675,49 +26675,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="C3" t="n">
-        <v>222</v>
+        <v>222.0974352168747</v>
       </c>
       <c r="D3" t="n">
-        <v>259</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="E3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="F3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="G3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="H3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="I3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="L3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="M3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="N3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="O3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="P3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="C3" t="n">
-        <v>199</v>
+        <v>199.0840525300854</v>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>38.69895730059008</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>59.02482598057778</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -30959,49 +30959,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09246231155778895</v>
+        <v>0.09251611130367558</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9469296482412066</v>
+        <v>0.9474806248887679</v>
       </c>
       <c r="I2" t="n">
-        <v>3.564653266331664</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8476231155779</v>
+        <v>7.852189301760344</v>
       </c>
       <c r="K2" t="n">
-        <v>11.76155276381911</v>
+        <v>11.76839629324494</v>
       </c>
       <c r="L2" t="n">
-        <v>14.5912462311558</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M2" t="n">
-        <v>16.23557286432163</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N2" t="n">
-        <v>16.49828140703519</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O2" t="n">
-        <v>15.57885929648243</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P2" t="n">
-        <v>13.29619597989952</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.984889447236188</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
-        <v>5.808135678391965</v>
+        <v>5.811515176679516</v>
       </c>
       <c r="S2" t="n">
-        <v>2.106984924623118</v>
+        <v>2.108210886332509</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4047537688442215</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U2" t="n">
-        <v>0.007396984924623117</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31038,49 +31038,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04947169811320762</v>
+        <v>0.0495004835149808</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4777924528301893</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I3" t="n">
-        <v>1.703301886792455</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J3" t="n">
-        <v>4.673990566037741</v>
+        <v>4.676710155246499</v>
       </c>
       <c r="K3" t="n">
-        <v>7.988594339622651</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L3" t="n">
-        <v>10.74165094339624</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M3" t="n">
-        <v>12.53500000000001</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N3" t="n">
-        <v>12.86676415094341</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O3" t="n">
-        <v>11.77057547169812</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P3" t="n">
-        <v>9.446924528301897</v>
+        <v>9.452421277522957</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.315018867924538</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R3" t="n">
-        <v>3.071584905660381</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9189150943396232</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1994056603773587</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003254716981132081</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31117,49 +31117,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0414754098360656</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3687540983606563</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I4" t="n">
-        <v>1.247278688524591</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J4" t="n">
-        <v>2.932311475409838</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K4" t="n">
-        <v>4.818688524590167</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L4" t="n">
-        <v>6.166262295081973</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M4" t="n">
-        <v>6.50145901639345</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N4" t="n">
-        <v>6.346868852459029</v>
+        <v>6.350561815847949</v>
       </c>
       <c r="O4" t="n">
-        <v>5.862360655737711</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P4" t="n">
-        <v>5.016262295081969</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.473000000000004</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R4" t="n">
-        <v>1.864885245901641</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7228032786885248</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1772131147540984</v>
+        <v>0.1773162272588684</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002262295081967218</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8924623115577891</v>
+        <v>0.8928540109221088</v>
       </c>
       <c r="H5" t="n">
-        <v>9.139929648241209</v>
+        <v>9.14394113935605</v>
       </c>
       <c r="I5" t="n">
-        <v>34.40665326633169</v>
+        <v>34.42175425607464</v>
       </c>
       <c r="J5" t="n">
-        <v>75.74662311557798</v>
+        <v>75.7798681095004</v>
       </c>
       <c r="K5" t="n">
-        <v>113.5245527638192</v>
+        <v>113.5743783918333</v>
       </c>
       <c r="L5" t="n">
-        <v>140.8372462311559</v>
+        <v>140.8990593285908</v>
       </c>
       <c r="M5" t="n">
-        <v>156.7085728643218</v>
+        <v>156.7773518453268</v>
       </c>
       <c r="N5" t="n">
-        <v>159.2442814070353</v>
+        <v>159.3141733038593</v>
       </c>
       <c r="O5" t="n">
-        <v>150.3698592964826</v>
+        <v>150.4358562327526</v>
       </c>
       <c r="P5" t="n">
-        <v>128.3371959798996</v>
+        <v>128.393522838113</v>
       </c>
       <c r="Q5" t="n">
-        <v>96.37588944723626</v>
+        <v>96.41818857196495</v>
       </c>
       <c r="R5" t="n">
-        <v>56.06113567839203</v>
+        <v>56.08574076358597</v>
       </c>
       <c r="S5" t="n">
-        <v>20.33698492462314</v>
+        <v>20.34591077388757</v>
       </c>
       <c r="T5" t="n">
-        <v>3.906753768844224</v>
+        <v>3.908468432811533</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0713969849246231</v>
+        <v>0.0714283208737687</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,49 +31275,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4775094339622646</v>
+        <v>0.4777190115985608</v>
       </c>
       <c r="H6" t="n">
-        <v>4.611735849056608</v>
+        <v>4.613759927807154</v>
       </c>
       <c r="I6" t="n">
-        <v>16.44056603773587</v>
+        <v>16.44778175898554</v>
       </c>
       <c r="J6" t="n">
-        <v>45.1141698113208</v>
+        <v>45.13397030194999</v>
       </c>
       <c r="K6" t="n">
-        <v>77.10730188679253</v>
+        <v>77.14114407905356</v>
       </c>
       <c r="L6" t="n">
-        <v>103.680283018868</v>
+        <v>103.7257880227489</v>
       </c>
       <c r="M6" t="n">
-        <v>120.9900000000001</v>
+        <v>121.0431021931967</v>
       </c>
       <c r="N6" t="n">
-        <v>124.192245283019</v>
+        <v>124.246752933259</v>
       </c>
       <c r="O6" t="n">
-        <v>113.6116415094341</v>
+        <v>113.6615053604698</v>
       </c>
       <c r="P6" t="n">
-        <v>91.18335849056612</v>
+        <v>91.22337862709711</v>
       </c>
       <c r="Q6" t="n">
-        <v>60.95366037735855</v>
+        <v>60.98041277879173</v>
       </c>
       <c r="R6" t="n">
-        <v>29.64747169811325</v>
+        <v>29.6604838955668</v>
       </c>
       <c r="S6" t="n">
-        <v>8.869528301886794</v>
+        <v>8.87342111456098</v>
       </c>
       <c r="T6" t="n">
-        <v>1.924698113207548</v>
+        <v>1.925542858153847</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03141509433962268</v>
+        <v>0.03142888234201059</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4003278688524593</v>
+        <v>0.400503571702561</v>
       </c>
       <c r="H7" t="n">
-        <v>3.559278688524596</v>
+        <v>3.560840846591863</v>
       </c>
       <c r="I7" t="n">
-        <v>12.03895081967215</v>
+        <v>12.04423468356429</v>
       </c>
       <c r="J7" t="n">
-        <v>28.30318032786888</v>
+        <v>28.31560251937106</v>
       </c>
       <c r="K7" t="n">
-        <v>46.51081967213117</v>
+        <v>46.53123314871571</v>
       </c>
       <c r="L7" t="n">
-        <v>59.51783606557383</v>
+        <v>59.54395828748803</v>
       </c>
       <c r="M7" t="n">
-        <v>62.75321311475414</v>
+        <v>62.78075533515689</v>
       </c>
       <c r="N7" t="n">
-        <v>61.26108196721321</v>
+        <v>61.28796929517467</v>
       </c>
       <c r="O7" t="n">
-        <v>56.58452459016401</v>
+        <v>56.60935938937655</v>
       </c>
       <c r="P7" t="n">
-        <v>48.41783606557379</v>
+        <v>48.43908652664426</v>
       </c>
       <c r="Q7" t="n">
-        <v>33.52200000000003</v>
+        <v>33.53671271774809</v>
       </c>
       <c r="R7" t="n">
-        <v>18.00019672131148</v>
+        <v>18.00809696037151</v>
       </c>
       <c r="S7" t="n">
-        <v>6.976622950819676</v>
+        <v>6.979684972307355</v>
       </c>
       <c r="T7" t="n">
-        <v>1.710491803278689</v>
+        <v>1.711242533638215</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02183606557377053</v>
+        <v>0.02184564936559426</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.041206030150753</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H8" t="n">
-        <v>10.6632512562814</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I8" t="n">
-        <v>40.14109547738694</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J8" t="n">
-        <v>88.37106030150755</v>
+        <v>88.98399123388617</v>
       </c>
       <c r="K8" t="n">
-        <v>132.445311557789</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L8" t="n">
-        <v>164.3101206030151</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M8" t="n">
-        <v>182.8266683417085</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N8" t="n">
-        <v>185.7849949748744</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O8" t="n">
-        <v>175.4315025125628</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P8" t="n">
-        <v>149.7267286432161</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q8" t="n">
-        <v>112.4385376884422</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R8" t="n">
-        <v>65.4046582914573</v>
+        <v>65.8582970511566</v>
       </c>
       <c r="S8" t="n">
-        <v>23.72648241206031</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T8" t="n">
-        <v>4.557879396984923</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08329648241206018</v>
+        <v>0.08387421668903385</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5570943396226413</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H9" t="n">
-        <v>5.380358490566038</v>
+        <v>5.417676003051488</v>
       </c>
       <c r="I9" t="n">
-        <v>19.18066037735849</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J9" t="n">
-        <v>52.63319811320756</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K9" t="n">
-        <v>89.95851886792457</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L9" t="n">
-        <v>120.9603301886793</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M9" t="n">
-        <v>141.155</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>131.3417120833365</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>132.5469150943397</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P9" t="n">
-        <v>106.3805849056604</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q9" t="n">
-        <v>71.11260377358494</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R9" t="n">
-        <v>34.58871698113209</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S9" t="n">
-        <v>10.34778301886792</v>
+        <v>10.41955398407041</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24548113207547</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03665094339622642</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4670491803278686</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H10" t="n">
-        <v>4.15249180327869</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I10" t="n">
-        <v>14.04544262295082</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J10" t="n">
-        <v>33.02037704918033</v>
+        <v>33.24940237062826</v>
       </c>
       <c r="K10" t="n">
-        <v>54.26262295081966</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L10" t="n">
-        <v>69.4374754098361</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M10" t="n">
-        <v>73.21208196721312</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N10" t="n">
-        <v>71.47126229508203</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O10" t="n">
-        <v>66.01527868852463</v>
+        <v>66.47315263707451</v>
       </c>
       <c r="P10" t="n">
-        <v>56.48747540983604</v>
+        <v>56.87926567298936</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.109</v>
+        <v>39.38025527013719</v>
       </c>
       <c r="R10" t="n">
-        <v>21.00022950819671</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S10" t="n">
-        <v>8.139393442622946</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T10" t="n">
-        <v>1.995573770491802</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02547540983606559</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.286432160804021</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H11" t="n">
-        <v>13.17467336683418</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I11" t="n">
-        <v>49.59517587939708</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J11" t="n">
-        <v>109.1843216080404</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K11" t="n">
-        <v>163.6389949748746</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L11" t="n">
-        <v>203.0086432160808</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M11" t="n">
-        <v>225.8862311557793</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N11" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>216.7493467336687</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P11" t="n">
-        <v>184.9905527638194</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q11" t="n">
-        <v>138.9202010050253</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R11" t="n">
-        <v>80.80884422110567</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S11" t="n">
-        <v>29.31457286432166</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T11" t="n">
-        <v>5.631356783919604</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1029145728643217</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,19 +31749,19 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6883018867924539</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H12" t="n">
-        <v>6.647547169811332</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I12" t="n">
-        <v>23.69811320754721</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J12" t="n">
-        <v>65.02943396226428</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K12" t="n">
-        <v>111.1456603773587</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>131.4354716981134</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q12" t="n">
-        <v>87.86113207547184</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R12" t="n">
-        <v>42.73509433962273</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S12" t="n">
-        <v>12.78490566037737</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T12" t="n">
-        <v>2.774339622641512</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04528301886792461</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5770491803278697</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1304918032787</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I13" t="n">
-        <v>17.35344262295085</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J13" t="n">
-        <v>40.79737704918038</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K13" t="n">
-        <v>67.04262295081976</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L13" t="n">
-        <v>85.7914754098362</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M13" t="n">
-        <v>90.45508196721322</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N13" t="n">
-        <v>88.30426229508215</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O13" t="n">
-        <v>81.56327868852473</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P13" t="n">
-        <v>69.79147540983614</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.32000000000009</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R13" t="n">
-        <v>25.94622950819675</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S13" t="n">
-        <v>10.05639344262296</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T13" t="n">
-        <v>2.465573770491806</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03147540983606566</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.286432160804021</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H14" t="n">
-        <v>13.17467336683419</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I14" t="n">
-        <v>49.5951758793971</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J14" t="n">
-        <v>109.1843216080404</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K14" t="n">
-        <v>163.6389949748747</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L14" t="n">
-        <v>203.0086432160808</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M14" t="n">
-        <v>225.8862311557793</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>216.7493467336688</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P14" t="n">
-        <v>184.9905527638195</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q14" t="n">
-        <v>138.9202010050254</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R14" t="n">
-        <v>80.8088442211057</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S14" t="n">
-        <v>29.31457286432168</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T14" t="n">
-        <v>5.631356783919608</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1029145728643217</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,19 +31986,19 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6883018867924543</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H15" t="n">
-        <v>6.647547169811336</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I15" t="n">
-        <v>23.69811320754722</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J15" t="n">
-        <v>65.02943396226429</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K15" t="n">
-        <v>111.1456603773587</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>131.4354716981135</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q15" t="n">
-        <v>87.8611320754719</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R15" t="n">
-        <v>42.73509433962274</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S15" t="n">
-        <v>12.78490566037738</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T15" t="n">
-        <v>2.774339622641514</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04528301886792464</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5770491803278698</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H16" t="n">
-        <v>5.130491803278701</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I16" t="n">
-        <v>17.35344262295085</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J16" t="n">
-        <v>40.7973770491804</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K16" t="n">
-        <v>67.04262295081978</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L16" t="n">
-        <v>85.79147540983622</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M16" t="n">
-        <v>90.45508196721327</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N16" t="n">
-        <v>88.30426229508221</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O16" t="n">
-        <v>81.56327868852476</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P16" t="n">
-        <v>69.79147540983615</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.3200000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R16" t="n">
-        <v>25.94622950819677</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S16" t="n">
-        <v>10.05639344262297</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T16" t="n">
-        <v>2.465573770491807</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03147540983606567</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.286432160804025</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H17" t="n">
-        <v>13.17467336683422</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I17" t="n">
-        <v>49.59517587939721</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J17" t="n">
-        <v>109.1843216080406</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K17" t="n">
-        <v>163.6389949748751</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L17" t="n">
-        <v>203.0086432160813</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M17" t="n">
-        <v>225.8862311557797</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635967183</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>216.7493467336692</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P17" t="n">
-        <v>184.9905527638199</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q17" t="n">
-        <v>138.9202010050257</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R17" t="n">
-        <v>80.8088442211059</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S17" t="n">
-        <v>29.31457286432172</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T17" t="n">
-        <v>5.63135678391962</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1029145728643219</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6883018867924559</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H18" t="n">
-        <v>6.647547169811348</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I18" t="n">
-        <v>23.69811320754728</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J18" t="n">
-        <v>65.02943396226446</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K18" t="n">
-        <v>111.1456603773589</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797800007</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339221363</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120834598</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444445711</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>131.4354716981138</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q18" t="n">
-        <v>87.8611320754721</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R18" t="n">
-        <v>42.73509433962285</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S18" t="n">
-        <v>12.7849056603774</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T18" t="n">
-        <v>2.77433962264152</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04528301886792473</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5770491803278716</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H19" t="n">
-        <v>5.130491803278714</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I19" t="n">
-        <v>17.3534426229509</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J19" t="n">
-        <v>40.7973770491805</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K19" t="n">
-        <v>67.04262295081995</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L19" t="n">
-        <v>85.79147540983645</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M19" t="n">
-        <v>90.45508196721347</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N19" t="n">
-        <v>88.30426229508241</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O19" t="n">
-        <v>81.56327868852496</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P19" t="n">
-        <v>69.79147540983635</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.32000000000021</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R19" t="n">
-        <v>25.94622950819682</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S19" t="n">
-        <v>10.05639344262299</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T19" t="n">
-        <v>2.465573770491813</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03147540983606575</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.286432160804025</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H20" t="n">
-        <v>13.17467336683422</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I20" t="n">
-        <v>49.59517587939721</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J20" t="n">
-        <v>109.1843216080407</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K20" t="n">
-        <v>163.6389949748752</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L20" t="n">
-        <v>203.0086432160813</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M20" t="n">
-        <v>225.8862311557799</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N20" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>216.7493467336693</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P20" t="n">
-        <v>184.9905527638199</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q20" t="n">
-        <v>138.9202010050258</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R20" t="n">
-        <v>80.80884422110596</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S20" t="n">
-        <v>29.31457286432178</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T20" t="n">
-        <v>5.631356783919622</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U20" t="n">
-        <v>0.102914572864322</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,19 +32460,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6883018867924561</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H21" t="n">
-        <v>6.647547169811352</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I21" t="n">
-        <v>23.69811320754728</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J21" t="n">
-        <v>65.02943396226452</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K21" t="n">
-        <v>111.145660377359</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>131.4354716981139</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q21" t="n">
-        <v>87.86113207547213</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R21" t="n">
-        <v>42.73509433962287</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S21" t="n">
-        <v>12.7849056603774</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T21" t="n">
-        <v>2.774339622641521</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04528301886792475</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5770491803278718</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H22" t="n">
-        <v>5.130491803278717</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I22" t="n">
-        <v>17.35344262295091</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J22" t="n">
-        <v>40.79737704918053</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K22" t="n">
-        <v>67.04262295082</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L22" t="n">
-        <v>85.79147540983648</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M22" t="n">
-        <v>90.4550819672135</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N22" t="n">
-        <v>88.30426229508244</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O22" t="n">
-        <v>81.56327868852502</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P22" t="n">
-        <v>69.79147540983638</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.32000000000021</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R22" t="n">
-        <v>25.94622950819682</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S22" t="n">
-        <v>10.056393442623</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T22" t="n">
-        <v>2.465573770491815</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03147540983606578</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.286432160804025</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H23" t="n">
-        <v>13.17467336683425</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I23" t="n">
-        <v>49.59517587939727</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J23" t="n">
-        <v>109.1843216080409</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K23" t="n">
-        <v>163.6389949748752</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L23" t="n">
-        <v>203.0086432160815</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M23" t="n">
-        <v>225.8862311557803</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N23" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>216.7493467336698</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P23" t="n">
-        <v>184.99055276382</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q23" t="n">
-        <v>138.9202010050259</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R23" t="n">
-        <v>80.80884422110596</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S23" t="n">
-        <v>29.31457286432179</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T23" t="n">
-        <v>5.631356783919625</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1029145728643222</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,19 +32697,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6883018867924565</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H24" t="n">
-        <v>6.647547169811363</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I24" t="n">
-        <v>23.6981132075473</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J24" t="n">
-        <v>65.02943396226458</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K24" t="n">
-        <v>111.1456603773592</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>131.435471698114</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q24" t="n">
-        <v>87.86113207547218</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R24" t="n">
-        <v>42.73509433962287</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S24" t="n">
-        <v>12.78490566037742</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T24" t="n">
-        <v>2.774339622641523</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04528301886792477</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.577049180327872</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H25" t="n">
-        <v>5.130491803278717</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I25" t="n">
-        <v>17.35344262295093</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J25" t="n">
-        <v>40.79737704918053</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K25" t="n">
-        <v>67.04262295082006</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L25" t="n">
-        <v>85.79147540983648</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M25" t="n">
-        <v>90.45508196721356</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N25" t="n">
-        <v>88.30426229508249</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O25" t="n">
-        <v>81.56327868852502</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P25" t="n">
-        <v>69.79147540983644</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q25" t="n">
-        <v>48.32000000000027</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R25" t="n">
-        <v>25.94622950819688</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S25" t="n">
-        <v>10.056393442623</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T25" t="n">
-        <v>2.465573770491815</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03147540983606581</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.286432160804032</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H26" t="n">
-        <v>13.1746733668343</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I26" t="n">
-        <v>49.59517587939752</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J26" t="n">
-        <v>109.1843216080414</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K26" t="n">
-        <v>163.638994974876</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L26" t="n">
-        <v>203.0086432160826</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M26" t="n">
-        <v>225.8862311557812</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635967199</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>216.7493467336707</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P26" t="n">
-        <v>184.9905527638208</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q26" t="n">
-        <v>138.9202010050265</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R26" t="n">
-        <v>80.80884422110636</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S26" t="n">
-        <v>29.31457286432191</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T26" t="n">
-        <v>5.63135678391965</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1029145728643226</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6883018867924596</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H27" t="n">
-        <v>6.647547169811391</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I27" t="n">
-        <v>23.69811320754743</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J27" t="n">
-        <v>65.02943396226475</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K27" t="n">
-        <v>111.1456603773597</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797800031</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>142.134033922157</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120834623</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444445734</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>131.4354716981146</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q27" t="n">
-        <v>87.86113207547258</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R27" t="n">
-        <v>42.7350943396231</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S27" t="n">
-        <v>12.78490566037749</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T27" t="n">
-        <v>2.774339622641536</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U27" t="n">
-        <v>0.045283018867925</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5770491803278742</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H28" t="n">
-        <v>5.130491803278742</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I28" t="n">
-        <v>17.353442622951</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J28" t="n">
-        <v>40.79737704918072</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K28" t="n">
-        <v>67.04262295082034</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L28" t="n">
-        <v>85.79147540983693</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M28" t="n">
-        <v>90.45508196721396</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N28" t="n">
-        <v>88.30426229508289</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O28" t="n">
-        <v>81.56327868852541</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P28" t="n">
-        <v>69.79147540983672</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q28" t="n">
-        <v>48.32000000000053</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R28" t="n">
-        <v>25.94622950819699</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S28" t="n">
-        <v>10.05639344262305</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T28" t="n">
-        <v>2.465573770491826</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U28" t="n">
-        <v>0.03147540983606589</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.286432160804039</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H29" t="n">
-        <v>13.17467336683435</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I29" t="n">
-        <v>49.59517587939775</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J29" t="n">
-        <v>109.184321608042</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K29" t="n">
-        <v>163.6389949748769</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L29" t="n">
-        <v>203.0086432160834</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M29" t="n">
-        <v>225.8862311557824</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N29" t="n">
-        <v>229.4130635968309</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>216.7493467336714</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P29" t="n">
-        <v>184.9905527638221</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q29" t="n">
-        <v>138.9202010050273</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R29" t="n">
-        <v>80.80884422110681</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S29" t="n">
-        <v>29.31457286432205</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T29" t="n">
-        <v>5.631356783919686</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U29" t="n">
-        <v>0.102914572864323</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6883018867924641</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H30" t="n">
-        <v>6.647547169811416</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I30" t="n">
-        <v>23.69811320754755</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J30" t="n">
-        <v>65.0294339622652</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K30" t="n">
-        <v>111.1456603773602</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797801154</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>142.134033922243</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>131.341712083558</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444446862</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>131.4354716981153</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q30" t="n">
-        <v>87.86113207547315</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R30" t="n">
-        <v>42.73509433962335</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S30" t="n">
-        <v>12.78490566037754</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T30" t="n">
-        <v>2.774339622641553</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U30" t="n">
-        <v>0.04528301886792527</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5770491803278782</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H31" t="n">
-        <v>5.130491803278771</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I31" t="n">
-        <v>17.3534426229511</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J31" t="n">
-        <v>40.79737704918095</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K31" t="n">
-        <v>67.04262295082069</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L31" t="n">
-        <v>85.79147540983745</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M31" t="n">
-        <v>90.45508196721453</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N31" t="n">
-        <v>88.30426229508346</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O31" t="n">
-        <v>81.56327868852587</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P31" t="n">
-        <v>69.79147540983712</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q31" t="n">
-        <v>48.32000000000075</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R31" t="n">
-        <v>25.94622950819709</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S31" t="n">
-        <v>10.0563934426231</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T31" t="n">
-        <v>2.46557377049184</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U31" t="n">
-        <v>0.03147540983606611</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.286432160804053</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H32" t="n">
-        <v>13.17467336683449</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I32" t="n">
-        <v>49.59517587939821</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J32" t="n">
-        <v>109.1843216080429</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K32" t="n">
-        <v>163.6389949748787</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L32" t="n">
-        <v>203.0086432160853</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M32" t="n">
-        <v>225.8862311557849</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N32" t="n">
-        <v>229.4130635967809</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>216.7493467336736</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P32" t="n">
-        <v>184.9905527638239</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q32" t="n">
-        <v>138.9202010050288</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R32" t="n">
-        <v>80.80884422110772</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S32" t="n">
-        <v>29.3145728643224</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T32" t="n">
-        <v>5.631356783919732</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1029145728643241</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6883018867924698</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H33" t="n">
-        <v>6.647547169811487</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I33" t="n">
-        <v>23.69811320754777</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J33" t="n">
-        <v>65.02943396226595</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K33" t="n">
-        <v>111.1456603773613</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797800789</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339222083</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120835376</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444446339</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>131.4354716981168</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q33" t="n">
-        <v>87.86113207547389</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R33" t="n">
-        <v>42.73509433962375</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S33" t="n">
-        <v>12.78490566037768</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T33" t="n">
-        <v>2.774339622641576</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U33" t="n">
-        <v>0.04528301886792572</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.577049180327884</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H34" t="n">
-        <v>5.130491803278828</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I34" t="n">
-        <v>17.35344262295128</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J34" t="n">
-        <v>40.79737704918141</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K34" t="n">
-        <v>67.04262295082147</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L34" t="n">
-        <v>85.79147540983824</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M34" t="n">
-        <v>90.45508196721526</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N34" t="n">
-        <v>88.3042622950842</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O34" t="n">
-        <v>81.56327868852678</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P34" t="n">
-        <v>69.79147540983789</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q34" t="n">
-        <v>48.32000000000121</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R34" t="n">
-        <v>25.94622950819737</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S34" t="n">
-        <v>10.05639344262322</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T34" t="n">
-        <v>2.46557377049187</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U34" t="n">
-        <v>0.03147540983606648</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.286432160804033</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H35" t="n">
-        <v>13.17467336683431</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I35" t="n">
-        <v>49.59517587939752</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J35" t="n">
-        <v>109.1843216080414</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K35" t="n">
-        <v>163.6389949748762</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L35" t="n">
-        <v>203.0086432160828</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M35" t="n">
-        <v>225.8862311557813</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635968874</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
-        <v>216.7493467336707</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P35" t="n">
-        <v>184.9905527638209</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q35" t="n">
-        <v>138.9202010050269</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R35" t="n">
-        <v>80.80884422110647</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S35" t="n">
-        <v>29.31457286432191</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T35" t="n">
-        <v>5.631356783919654</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1029145728643227</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6883018867924601</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H36" t="n">
-        <v>6.647547169811395</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I36" t="n">
-        <v>23.6981132075474</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J36" t="n">
-        <v>65.02943396226487</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K36" t="n">
-        <v>111.1456603773597</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797801502</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339222948</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120836098</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>142.5962444447205</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>131.4354716981146</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q36" t="n">
-        <v>87.86113207547264</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R36" t="n">
-        <v>42.73509433962312</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S36" t="n">
-        <v>12.7849056603775</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T36" t="n">
-        <v>2.774339622641537</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U36" t="n">
-        <v>0.045283018867925</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5770491803278758</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H37" t="n">
-        <v>5.130491803278749</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I37" t="n">
-        <v>17.35344262295105</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J37" t="n">
-        <v>40.79737704918078</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K37" t="n">
-        <v>67.04262295082042</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L37" t="n">
-        <v>85.79147540983699</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M37" t="n">
-        <v>90.45508196721401</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N37" t="n">
-        <v>88.30426229508295</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O37" t="n">
-        <v>81.56327868852553</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P37" t="n">
-        <v>69.79147540983692</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q37" t="n">
-        <v>48.32000000000053</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R37" t="n">
-        <v>25.946229508197</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S37" t="n">
-        <v>10.05639344262306</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T37" t="n">
-        <v>2.465573770491831</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U37" t="n">
-        <v>0.03147540983606593</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.286432160804044</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H38" t="n">
-        <v>13.17467336683441</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I38" t="n">
-        <v>49.59517587939798</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J38" t="n">
-        <v>109.1843216080423</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K38" t="n">
-        <v>163.6389949748775</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L38" t="n">
-        <v>203.0086432160844</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M38" t="n">
-        <v>225.8862311557834</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N38" t="n">
-        <v>229.4130635969969</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>216.7493467336726</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P38" t="n">
-        <v>184.990552763823</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q38" t="n">
-        <v>138.9202010050283</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R38" t="n">
-        <v>80.80884422110712</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S38" t="n">
-        <v>29.31457286432221</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T38" t="n">
-        <v>5.631356783919718</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1029145728643235</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6883018867924672</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H39" t="n">
-        <v>6.647547169811446</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I39" t="n">
-        <v>23.69811320754766</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J39" t="n">
-        <v>65.02943396226547</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K39" t="n">
-        <v>111.1456603773606</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797803133</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339224529</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120837393</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>142.5962444448827</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>131.4354716981159</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q39" t="n">
-        <v>87.86113207547352</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R39" t="n">
-        <v>42.73509433962351</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S39" t="n">
-        <v>12.7849056603776</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T39" t="n">
-        <v>2.774339622641566</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U39" t="n">
-        <v>0.0452830188679255</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5770491803278811</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H40" t="n">
-        <v>5.13049180327879</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I40" t="n">
-        <v>17.35344262295122</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J40" t="n">
-        <v>40.79737704918111</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K40" t="n">
-        <v>67.04262295082123</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L40" t="n">
-        <v>85.79147540983776</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M40" t="n">
-        <v>90.45508196721504</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N40" t="n">
-        <v>88.30426229508386</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O40" t="n">
-        <v>81.56327868852618</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P40" t="n">
-        <v>69.7914754098376</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q40" t="n">
-        <v>48.32000000000098</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R40" t="n">
-        <v>25.9462295081972</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S40" t="n">
-        <v>10.05639344262314</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T40" t="n">
-        <v>2.465573770491852</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U40" t="n">
-        <v>0.03147540983606625</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.286432160804038</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H41" t="n">
-        <v>13.17467336683437</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I41" t="n">
-        <v>49.59517587939776</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J41" t="n">
-        <v>109.1843216080419</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K41" t="n">
-        <v>163.6389949748768</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L41" t="n">
-        <v>203.0086432160838</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M41" t="n">
-        <v>225.8862311557827</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N41" t="n">
-        <v>229.4130635971901</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>216.7493467336717</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P41" t="n">
-        <v>184.9905527638217</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q41" t="n">
-        <v>138.920201005027</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R41" t="n">
-        <v>80.80884422110675</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S41" t="n">
-        <v>29.31457286432209</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T41" t="n">
-        <v>5.631356783919677</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1029145728643232</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.688301886792463</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H42" t="n">
-        <v>6.647547169811427</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I42" t="n">
-        <v>23.69811320754753</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J42" t="n">
-        <v>65.02943396226512</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K42" t="n">
-        <v>111.1456603773602</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797804733</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339226175</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120839325</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444450757</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>131.4354716981151</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q42" t="n">
-        <v>87.86113207547301</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R42" t="n">
-        <v>42.73509433962328</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S42" t="n">
-        <v>12.78490566037756</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T42" t="n">
-        <v>2.774339622641549</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U42" t="n">
-        <v>0.04528301886792518</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5770491803278773</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H43" t="n">
-        <v>5.130491803278767</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I43" t="n">
-        <v>17.35344262295106</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J43" t="n">
-        <v>40.79737704918092</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K43" t="n">
-        <v>67.0426229508206</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L43" t="n">
-        <v>85.7914754098373</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M43" t="n">
-        <v>90.45508196721438</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N43" t="n">
-        <v>88.30426229508332</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O43" t="n">
-        <v>81.56327868852581</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P43" t="n">
-        <v>69.79147540983698</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q43" t="n">
-        <v>48.32000000000071</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R43" t="n">
-        <v>25.94622950819713</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S43" t="n">
-        <v>10.0563934426231</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T43" t="n">
-        <v>2.46557377049184</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U43" t="n">
-        <v>0.03147540983606607</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.286432160804053</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H44" t="n">
-        <v>13.17467336683456</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I44" t="n">
-        <v>49.59517587939825</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J44" t="n">
-        <v>109.1843216080434</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K44" t="n">
-        <v>163.6389949748787</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L44" t="n">
-        <v>203.0086432160868</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M44" t="n">
-        <v>225.8862311557853</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N44" t="n">
-        <v>229.4130635972728</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>216.7493467336747</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P44" t="n">
-        <v>184.9905527638241</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q44" t="n">
-        <v>138.9202010050292</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R44" t="n">
-        <v>80.80884422110769</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S44" t="n">
-        <v>29.31457286432241</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T44" t="n">
-        <v>5.631356783919752</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1029145728643246</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6883018867924723</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H45" t="n">
-        <v>6.647547169811521</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I45" t="n">
-        <v>23.6981132075478</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J45" t="n">
-        <v>65.02943396226603</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K45" t="n">
-        <v>111.1456603773617</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L45" t="n">
-        <v>138.5543797805577</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
-        <v>142.1340339227002</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N45" t="n">
-        <v>131.3417120840161</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>142.5962444450919</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>131.4354716981169</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q45" t="n">
-        <v>87.8611320754742</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R45" t="n">
-        <v>42.73509433962379</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S45" t="n">
-        <v>12.78490566037775</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T45" t="n">
-        <v>2.774339622641586</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04528301886792576</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5770491803278849</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H46" t="n">
-        <v>5.130491803278826</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I46" t="n">
-        <v>17.35344262295132</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J46" t="n">
-        <v>40.79737704918139</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K46" t="n">
-        <v>67.04262295082154</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L46" t="n">
-        <v>85.79147540983844</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M46" t="n">
-        <v>90.45508196721558</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N46" t="n">
-        <v>88.30426229508451</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O46" t="n">
-        <v>81.56327868852675</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P46" t="n">
-        <v>69.79147540983809</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q46" t="n">
-        <v>48.32000000000125</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R46" t="n">
-        <v>25.94622950819751</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S46" t="n">
-        <v>10.05639344262321</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T46" t="n">
-        <v>2.465573770491869</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U46" t="n">
-        <v>0.03147540983606646</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
